--- a/docs/kerberos-library-comparison.xlsx
+++ b/docs/kerberos-library-comparison.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
   <si>
-    <t xml:space="preserve">shared-home-kerberos: Kerberos library options for krb-credd</t>
+    <t xml:space="preserve">shared-home-kerberos: Kerberos library options for orthrus</t>
   </si>
   <si>
     <t xml:space="preserve">Can each option mint per-user service tickets by constrained delegation and write them to the user's shared home? Compiled 2026-10-09.</t>
